--- a/artfynd/A 41184-2022 artfynd.xlsx
+++ b/artfynd/A 41184-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -774,6 +774,103 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>126637374</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78739</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björnhusberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>620233</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7045181</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Örnsköldsvik</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Anundsjö</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-07-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anders Malmsten</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 41184-2022 artfynd.xlsx
+++ b/artfynd/A 41184-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126637374</v>
       </c>
       <c r="B3" t="n">
-        <v>78739</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41184-2022 artfynd.xlsx
+++ b/artfynd/A 41184-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126637374</v>
       </c>
       <c r="B3" t="n">
-        <v>78770</v>
+        <v>78773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41184-2022 artfynd.xlsx
+++ b/artfynd/A 41184-2022 artfynd.xlsx
@@ -780,7 +780,7 @@
         <v>126637374</v>
       </c>
       <c r="B3" t="n">
-        <v>78773</v>
+        <v>78770</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 41184-2022 artfynd.xlsx
+++ b/artfynd/A 41184-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116085576</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/116086192</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,8 +978,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126637374</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>